--- a/daily_matches/job_matches_2026-04-04.xlsx
+++ b/daily_matches/job_matches_2026-04-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack &amp; AI Engineering Intern - Denver On-Site</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GESTURE</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, BigQuery, FastAPI, Docker, CI/CD</t>
+          <t>AI Engineer, Data Scientist, LangChain, Hugging Face, TensorFlow, PyTorch, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9bd7f54a3825f2</t>
+          <t>https://www.indeed.com/viewjob?jk=170d4c1d3d53f45f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Full Stack Developer (React)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Parts Authority</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, TensorFlow, PyTorch, FastAPI, Kubernetes</t>
+          <t>RAG, Gemini, Data Lake, MLflow, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9869277c38af1c</t>
+          <t>https://www.indeed.com/viewjob?jk=f34688127cc2aa8a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>C2 SMART Integration Engineer (Data Tagging and Availability)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>I4DM</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>RAG, S3, Glue, Synapse, Docker, Kubernetes, Apache Airflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f937871abc0131b7</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01c8b8d0caf9fe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Software Engineer - AI Agentic Product Dev Team (US)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Millennium Systems International</t>
+          <t>Eightfold</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Tableau, Power BI, Quicksight</t>
+          <t>RAG, S3, Redshift, Docker, Apache Airflow, Redshift, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb604cce16197b9</t>
+          <t>https://www.indeed.com/viewjob?jk=bd50de7c7c09c2ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60154e4c61c165c0</t>
+          <t>https://www.indeed.com/viewjob?jk=79050ec6925ece8b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>HealthEdge Software, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877c428e451eb94c</t>
+          <t>https://www.indeed.com/viewjob?jk=5abe1c65278c5c5c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I - Global Servicing Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Jenkins, Git, Kafka, NoSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb82a9de01e4b89c</t>
+          <t>https://www.indeed.com/viewjob?jk=68b3e994bb25291e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>AI Technical Partner Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vision Technologies, Inc</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Glen Burnie, MD, US USA</t>
+          <t>Hopkinton, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Quicksight, Python</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a12a89b7c9a6dc9e</t>
+          <t>https://www.indeed.com/viewjob?jk=413ec66594abf4e8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-2</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>National Vision, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kinesis, MLflow, FastAPI, CI/CD, Git, Snowflake, Kafka, Power BI, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,339 +776,339 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=389562e8f66ac66e</t>
+          <t>https://www.indeed.com/viewjob?jk=b05020b2a0b488f7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Keras, BigQuery, BigQuery, Python, SQL</t>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, MLflow, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=978faf75eab8459a</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd8c74793b9456b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Artificial Intelligence &amp; Automation Engineer</t>
+          <t>Cloud MLOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5599af9b653f0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=4413578d265ced61</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Cloud MLOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Python</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455da78c98681620</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6838ae00e17b03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Business Intelligence (BI) Engineer</t>
+          <t>Cloud MLOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>WhiteWater Express Car Wash</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Snowflake, MySQL, Tableau, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445f95617028d321</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e94e7777f29d75</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud MLOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Keene, NH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66405642daaaa86b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad1f726da18d47c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud MLOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c98d14af7164f47</t>
+          <t>https://www.indeed.com/viewjob?jk=0ceffca58a409922</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud MLOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff634a2dda844bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=da5c98d22f34e1ef</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Cloud MLOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, NoSQL, Tableau, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Python, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a1b8821fbe2a2e</t>
+          <t>https://www.indeed.com/viewjob?jk=09b0f25db2922813</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>.Net Full Stack developer</t>
+          <t>Cloud MLOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>American Family Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Saint Joseph, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, GitHub Actions, Git, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, PySpark, Python, R, Java</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=740dc49dc803bb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6a7bf6d85b8f0f1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer-Public Cloud</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ensono</t>
+          <t>Red Oak Counseling, Ltd</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Python, R, Scala</t>
+          <t>RAG, Copilot, S3, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e887dd787bceb5c0</t>
+          <t>https://www.indeed.com/viewjob?jk=24174db2e70ef62c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Analyst, Marketing Channel Insights</t>
+          <t>Data Scientist – Agentic AI (Enterprise Risk Management &amp; AI Governance)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crate and Barrel</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization, Hypothesis Testing, A/B Testing</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, PyTorch, Docker, CI/CD, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef2e51637f51336</t>
+          <t>https://www.indeed.com/viewjob?jk=b9bd042710e4b5e3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Global Commercial Services Technology</t>
+          <t>AI Models MAD - Model Automation and Dashboarding</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c815ee637f2a70bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0743eaeac6dd269e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Development Engineer, AI Open-Source Software</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ef67f6728a17b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2fc0e44941560982</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, Digital Experience</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DTN</t>
+          <t>New American Funding</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Python, R, Java, Scala, Optimization, A/B Testing</t>
+          <t>AI Engineer, RAG, Snowflake, Databricks, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,77 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1961685687c3dc1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Engineer I, Automation and Custom Applications</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Magnite</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>RAG, Docker, AKS, PostgreSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c052cc9d331c4364</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>FLEX Customer 360, Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Marriott International</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, S3, Snowflake, Cassandra, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c72db296370799da</t>
+          <t>https://www.indeed.com/viewjob?jk=60039525165c27b0</t>
         </is>
       </c>
     </row>
